--- a/data/DatosGrafica_AdquirirQ1_20260923_092405.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260923_092405.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectoTesis\ModelosBJT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E6FBFC-5337-4D31-B30F-1A6F6A1C82B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED72C990-9614-4858-A04C-9353F36BE3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -494,8 +494,8 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - (INDEX(A:A, MATCH(MODE(D:D), D:D,0))*1)</f>
-        <v>92</v>
+        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - G4</f>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
